--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_48.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4469246.640635231</v>
+        <v>4505604.686942447</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.537011709411</v>
+        <v>603.5370117101741</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.537011709411</v>
+        <v>603.5370117101741</v>
       </c>
     </row>
     <row r="11">
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
@@ -790,16 +790,16 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V3" t="n">
-        <v>252.2594777179801</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>129.4210794739357</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
         <v>184.8805867536895</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>120.0606009062724</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>68.52661386969076</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>288.6859759010486</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>374</v>
       </c>
       <c r="T9" t="n">
         <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>125.6231283450628</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
         <v>374</v>
       </c>
       <c r="W9" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
@@ -1453,19 +1453,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I12" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,31 +1489,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797057</v>
+        <v>305.4120422616786</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>303.4740340942942</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N13" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O13" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243966</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
         <v>72.84688483418068</v>
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>195.2639131038858</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,22 +1732,22 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
         <v>78.39139276613435</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1802,16 +1802,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -1930,7 +1930,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1975,16 +1975,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968766</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2030,7 +2030,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M19" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N19" t="n">
         <v>155.2579933044718</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T20" t="n">
         <v>259.6218731858503</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2200,31 +2200,31 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>173.3546605387601</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090244326</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>237.1483725282995</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
         <v>3.99961134672543</v>
@@ -2455,13 +2455,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>284.9649587918013</v>
       </c>
       <c r="X24" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2522,7 +2522,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090244506</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>195.2639131038854</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2680,25 +2680,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797057</v>
+        <v>305.4120422616786</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2750,16 +2750,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N31" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O31" t="n">
         <v>231.765039488851</v>
@@ -3045,7 +3045,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>237.1483725282995</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
@@ -3160,13 +3160,13 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968766</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>98.86273944538755</v>
@@ -3276,10 +3276,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3349,16 +3349,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3385,25 +3385,25 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>501.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>226.7834941523317</v>
+        <v>305.4120422616788</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>98.86273944538755</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T38" t="n">
         <v>259.6218731858503</v>
@@ -3583,7 +3583,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>26.93768689770263</v>
+        <v>200.5295027796754</v>
       </c>
       <c r="E39" t="n">
         <v>21.67209722191262</v>
@@ -3592,13 +3592,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
-        <v>94.96326777262568</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
@@ -3643,10 +3643,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
         <v>72.84688483418068</v>
@@ -3817,10 +3817,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
@@ -3829,13 +3829,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>94.96326777262591</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,31 +3859,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>18.63624233787687</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>226.7834941523314</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
@@ -4114,7 +4114,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>98.86273944538755</v>
@@ -4178,10 +4178,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>376.8716854102422</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>770.4399999999999</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M2" t="n">
-        <v>1140.7</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>1140.7</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O2" t="n">
-        <v>1140.7</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P2" t="n">
-        <v>1198.791891866258</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>596.2756859992882</v>
+        <v>590.9569085489952</v>
       </c>
       <c r="C3" t="n">
-        <v>596.2756859992882</v>
+        <v>590.9569085489952</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>590.9569085489952</v>
       </c>
       <c r="E3" t="n">
         <v>244.8234770117097</v>
@@ -4424,28 +4424,28 @@
         <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>971.6833037965423</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>908.5632923971827</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>904.0446616266809</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>903.8467567802944</v>
+        <v>769.042655594737</v>
       </c>
       <c r="V3" t="n">
-        <v>649.0392035298095</v>
+        <v>754.3854160073429</v>
       </c>
       <c r="W3" t="n">
-        <v>616.3390591764473</v>
+        <v>721.6852716539807</v>
       </c>
       <c r="X3" t="n">
-        <v>596.2756859992882</v>
+        <v>590.9569085489952</v>
       </c>
       <c r="Y3" t="n">
-        <v>596.2756859992882</v>
+        <v>590.9569085489952</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>633.3948269011844</v>
+        <v>664.2226252408586</v>
       </c>
       <c r="C4" t="n">
-        <v>759.3968327196202</v>
+        <v>790.2246310592944</v>
       </c>
       <c r="D4" t="n">
-        <v>872.7159768446203</v>
+        <v>903.5437751842945</v>
       </c>
       <c r="E4" t="n">
-        <v>990.5448810560333</v>
+        <v>1021.372679395708</v>
       </c>
       <c r="F4" t="n">
-        <v>1114.905853647969</v>
+        <v>1021.372679395708</v>
       </c>
       <c r="G4" t="n">
-        <v>1268.494514616821</v>
+        <v>1021.372679395708</v>
       </c>
       <c r="H4" t="n">
-        <v>1382.983127881912</v>
+        <v>1192.508255374777</v>
       </c>
       <c r="I4" t="n">
-        <v>1382.983127881912</v>
+        <v>1192.508255374777</v>
       </c>
       <c r="J4" t="n">
         <v>1382.983127881912</v>
@@ -4509,22 +4509,22 @@
         <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V4" t="n">
-        <v>259.1973975316665</v>
+        <v>269.1650686358568</v>
       </c>
       <c r="W4" t="n">
-        <v>259.1973975316665</v>
+        <v>441.0559868955343</v>
       </c>
       <c r="X4" t="n">
-        <v>410.22818855586</v>
+        <v>441.0559868955343</v>
       </c>
       <c r="Y4" t="n">
-        <v>521.6374892348923</v>
+        <v>552.4652875745666</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>464.2419149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1204.761914974874</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O5" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1262.853806841132</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>723.4756081758906</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="C6" t="n">
-        <v>358.7282218672851</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="D6" t="n">
-        <v>358.7282218672851</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="E6" t="n">
-        <v>358.7282218672851</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="F6" t="n">
-        <v>358.7282218672851</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="H6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1371.512696119776</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1236.510690087832</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>1173.390678688472</v>
+        <v>1142.026304022335</v>
       </c>
       <c r="T6" t="n">
-        <v>1168.87204791797</v>
+        <v>1137.507673251833</v>
       </c>
       <c r="U6" t="n">
-        <v>1168.674143071584</v>
+        <v>1137.309768405447</v>
       </c>
       <c r="V6" t="n">
-        <v>1154.01690348419</v>
+        <v>1122.652528818053</v>
       </c>
       <c r="W6" t="n">
-        <v>1121.316759130827</v>
+        <v>1089.952384464691</v>
       </c>
       <c r="X6" t="n">
-        <v>1101.253385953668</v>
+        <v>1069.889011287532</v>
       </c>
       <c r="Y6" t="n">
-        <v>1101.253385953668</v>
+        <v>692.1112335097536</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>576.7478641872053</v>
+        <v>460.8081946749797</v>
       </c>
       <c r="C7" t="n">
-        <v>702.7498700056411</v>
+        <v>586.8102004934156</v>
       </c>
       <c r="D7" t="n">
-        <v>816.0690141306412</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="E7" t="n">
-        <v>933.8979183420543</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="F7" t="n">
-        <v>1058.25889093399</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="G7" t="n">
-        <v>1211.847551902842</v>
+        <v>853.7180055872682</v>
       </c>
       <c r="H7" t="n">
-        <v>1382.983127881912</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I7" t="n">
-        <v>1382.983127881912</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J7" t="n">
-        <v>1382.983127881912</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
         <v>1382.983127881912</v>
@@ -4746,22 +4746,22 @@
         <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>214.2470695776767</v>
       </c>
       <c r="U7" t="n">
-        <v>266.1691336349672</v>
+        <v>460.8081946749797</v>
       </c>
       <c r="V7" t="n">
-        <v>464.9905265209132</v>
+        <v>460.8081946749797</v>
       </c>
       <c r="W7" t="n">
-        <v>464.9905265209132</v>
+        <v>460.8081946749797</v>
       </c>
       <c r="X7" t="n">
-        <v>464.9905265209132</v>
+        <v>460.8081946749797</v>
       </c>
       <c r="Y7" t="n">
-        <v>464.9905265209132</v>
+        <v>460.8081946749797</v>
       </c>
     </row>
     <row r="8">
@@ -4801,16 +4801,16 @@
         <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M8" t="n">
-        <v>886.1402453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>886.1402453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>886.1402453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1054.645116083211</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>676.8673383054328</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>672.3487075349309</v>
       </c>
       <c r="U9" t="n">
-        <v>1163.253333333334</v>
+        <v>672.1508026885444</v>
       </c>
       <c r="V9" t="n">
-        <v>785.4755555555557</v>
+        <v>294.3730249107666</v>
       </c>
       <c r="W9" t="n">
-        <v>407.6977777777778</v>
+        <v>261.6728805574044</v>
       </c>
       <c r="X9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="C10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="D10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="E10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="F10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="G10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="H10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="I10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4995,10 +4995,10 @@
         <v>876.4708337745928</v>
       </c>
       <c r="X10" t="n">
-        <v>1027.501624798786</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="Y10" t="n">
-        <v>1138.910925477819</v>
+        <v>1016.483548464727</v>
       </c>
     </row>
     <row r="11">
@@ -5020,7 +5020,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G11" t="n">
         <v>125.5027119537179</v>
@@ -5038,19 +5038,19 @@
         <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>1417.990475851726</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M11" t="n">
-        <v>1651.83297330616</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="N11" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>362.0396347695416</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C12" t="n">
-        <v>321.5346727033605</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D12" t="n">
-        <v>294.3248879582063</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E12" t="n">
-        <v>272.4338806633451</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F12" t="n">
-        <v>253.6093934533685</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G12" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H12" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>1658.367018159816</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1525.215274341931</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T12" t="n">
-        <v>1443.01795098519</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U12" t="n">
-        <v>1136.478522607115</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V12" t="n">
-        <v>1042.023303221741</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W12" t="n">
-        <v>929.5251790703987</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X12" t="n">
-        <v>829.6638260952598</v>
+        <v>960.319468324315</v>
       </c>
       <c r="Y12" t="n">
-        <v>426.2381768365382</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="13">
@@ -5172,49 +5172,49 @@
         <v>734.4361027208327</v>
       </c>
       <c r="D13" t="n">
-        <v>769.545246845834</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E13" t="n">
-        <v>809.164151057247</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F13" t="n">
-        <v>855.3151236491824</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G13" t="n">
-        <v>931.1258141262316</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.892525187269</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.283805434827</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J13" t="n">
-        <v>1515.576154611868</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K13" t="n">
-        <v>1619.080700024147</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405757</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.22798246859</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605487</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111698</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645225</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881608</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R13" t="n">
-        <v>81.9448594974138</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5257,7 +5257,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G14" t="n">
         <v>125.5027119537179</v>
@@ -5269,25 +5269,25 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L14" t="n">
-        <v>950.0896384907273</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M14" t="n">
-        <v>1592.599638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>668.0405455662465</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C15" t="n">
-        <v>303.2931592576411</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D15" t="n">
-        <v>276.0833745124869</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5378,7 +5378,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
         <v>1766.721857646244</v>
@@ -5387,13 +5387,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>811.4223126495403</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y15" t="n">
-        <v>732.239087633243</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="16">
@@ -5433,25 +5433,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O16" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q16" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R16" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C17" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D17" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E17" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F17" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G17" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5509,49 +5509,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L17" t="n">
-        <v>991.9887866314309</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M17" t="n">
-        <v>1634.498786631431</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N17" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O17" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P17" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X17" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C18" t="n">
-        <v>776.43273917484</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D18" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5618,19 +5618,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V18" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W18" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X18" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y18" t="n">
-        <v>1380.723936118091</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="19">
@@ -5673,22 +5673,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5731,7 +5731,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G20" t="n">
         <v>125.5027119537179</v>
@@ -5746,13 +5746,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L20" t="n">
-        <v>1418.446838088717</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M20" t="n">
-        <v>2060.956838088718</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N20" t="n">
         <v>2238.277892278425</v>
@@ -5767,7 +5767,7 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
         <v>2451.762030971221</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1316.525394051095</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D21" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E21" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5843,31 +5843,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R21" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S21" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U21" t="n">
-        <v>1766.721857646244</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V21" t="n">
-        <v>1672.26663826087</v>
+        <v>944.3590139079936</v>
       </c>
       <c r="W21" t="n">
-        <v>1559.768514109528</v>
+        <v>831.8608897566517</v>
       </c>
       <c r="X21" t="n">
-        <v>1459.907161134389</v>
+        <v>407.7571125390884</v>
       </c>
       <c r="Y21" t="n">
-        <v>1380.723936118091</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="22">
@@ -5880,52 +5880,52 @@
         <v>686.6440969023969</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4361027208375</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5452468458376</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E22" t="n">
-        <v>809.1641510572506</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F22" t="n">
-        <v>855.315123649186</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1258141262352</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H22" t="n">
-        <v>1027.892525187272</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.283805434831</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J22" t="n">
-        <v>1515.576154611872</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K22" t="n">
-        <v>1619.08070002415</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L22" t="n">
-        <v>1608.654647405761</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M22" t="n">
-        <v>1505.227982468593</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605491</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111702</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645261</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881645</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741744</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5980,25 +5980,25 @@
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>737.2059437357115</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L23" t="n">
-        <v>953.2578922784251</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M23" t="n">
-        <v>1595.767892278425</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N23" t="n">
-        <v>2238.277892278425</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O23" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1141.180125483445</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D24" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F24" t="n">
         <v>60.0226114399994</v>
@@ -6098,13 +6098,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X24" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y24" t="n">
-        <v>1380.723936118091</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="25">
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>686.6440969024035</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C25" t="n">
-        <v>734.4361027208392</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D25" t="n">
-        <v>769.5452468458393</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E25" t="n">
-        <v>809.1641510572523</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F25" t="n">
-        <v>855.3151236491877</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1258141262369</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.892525187274</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.283805434832</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J25" t="n">
-        <v>1515.576154611874</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K25" t="n">
-        <v>1619.080700024152</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1608.654647405763</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468595</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605493</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111704</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645279</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881663</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741926</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6183,7 +6183,7 @@
         <v>619.8974585570725</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.0967592361113</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="26">
@@ -6193,40 +6193,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D26" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H26" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L26" t="n">
-        <v>1376.091327711023</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M26" t="n">
-        <v>1376.091327711023</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N26" t="n">
         <v>1651.83297330616</v>
@@ -6253,16 +6253,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W26" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>668.040545566246</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C27" t="n">
-        <v>627.5355835000649</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D27" t="n">
-        <v>276.0833745124865</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E27" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F27" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6323,25 +6323,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S27" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W27" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X27" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y27" t="n">
-        <v>1056.481511875667</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N28" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
@@ -6463,43 +6463,43 @@
         <v>991.9887866314309</v>
       </c>
       <c r="M29" t="n">
-        <v>1009.32297330616</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N29" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O29" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P29" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="30">
@@ -6618,10 +6618,10 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M31" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N31" t="n">
         <v>1349.248439584877</v>
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G32" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H32" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L32" t="n">
-        <v>1376.091327711023</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M32" t="n">
-        <v>1376.091327711023</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="33">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1141.180125483445</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C33" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E33" t="n">
         <v>78.84709864997603</v>
@@ -6803,19 +6803,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W33" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X33" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y33" t="n">
-        <v>1380.723936118091</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="34">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C35" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D35" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E35" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G35" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
         <v>51.92</v>
@@ -6928,52 +6928,52 @@
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L35" t="n">
-        <v>991.9887866314309</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M35" t="n">
-        <v>1634.498786631431</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N35" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O35" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P35" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S35" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W35" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>816.937701241021</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C36" t="n">
-        <v>776.43273917484</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D36" t="n">
-        <v>749.2229544296858</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E36" t="n">
         <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7028,16 +7028,16 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1658.367018159816</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S36" t="n">
         <v>1429.292781642309</v>
       </c>
       <c r="T36" t="n">
-        <v>1347.095458285567</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U36" t="n">
         <v>1267.13416483617</v>
@@ -7046,13 +7046,13 @@
         <v>1172.678945450796</v>
       </c>
       <c r="W36" t="n">
-        <v>1060.180821299454</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X36" t="n">
-        <v>960.3194683243149</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y36" t="n">
-        <v>881.1362433080176</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="37">
@@ -7104,13 +7104,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7153,7 +7153,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G38" t="n">
         <v>125.5027119537179</v>
@@ -7165,31 +7165,31 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>1418.446838088717</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M38" t="n">
-        <v>1792.359898617045</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N38" t="n">
-        <v>1792.359898617045</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O38" t="n">
-        <v>1953.49</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P38" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S38" t="n">
         <v>2451.762030971221</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>912.8601939406431</v>
+        <v>992.2829698086704</v>
       </c>
       <c r="C39" t="n">
-        <v>548.1128076320376</v>
+        <v>627.5355835000651</v>
       </c>
       <c r="D39" t="n">
-        <v>520.9030228868835</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E39" t="n">
-        <v>499.0120155920222</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>155.9451041396213</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G39" t="n">
-        <v>151.9050926782825</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H39" t="n">
-        <v>147.8424926996219</v>
+        <v>51.92</v>
       </c>
       <c r="I39" t="n">
         <v>51.92</v>
@@ -7265,31 +7265,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q39" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R39" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U39" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>1056.241961023937</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y39" t="n">
-        <v>977.0587360076396</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="40">
@@ -7341,13 +7341,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7390,7 +7390,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
         <v>125.5027119537179</v>
@@ -7408,19 +7408,19 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>1418.446838088717</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M41" t="n">
-        <v>2060.956838088718</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N41" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>168.4528527561725</v>
+        <v>912.8601939406433</v>
       </c>
       <c r="C42" t="n">
-        <v>127.9478906899915</v>
+        <v>548.1128076320379</v>
       </c>
       <c r="D42" t="n">
-        <v>100.7381059448373</v>
+        <v>196.6605986444594</v>
       </c>
       <c r="E42" t="n">
-        <v>78.84709864997603</v>
+        <v>174.7695913495982</v>
       </c>
       <c r="F42" t="n">
-        <v>60.0226114399994</v>
+        <v>155.9451041396215</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866058</v>
+        <v>151.9050926782827</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>147.8424926996221</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095641</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U42" t="n">
-        <v>1766.721857646244</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V42" t="n">
-        <v>1348.024214018445</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W42" t="n">
-        <v>911.2836656246791</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X42" t="n">
-        <v>487.1798884071159</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y42" t="n">
-        <v>232.6513948231691</v>
+        <v>977.0587360076398</v>
       </c>
     </row>
     <row r="43">
@@ -7578,13 +7578,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C44" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D44" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E44" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G44" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H44" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
@@ -7642,19 +7642,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L44" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M44" t="n">
-        <v>1418.446838088717</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N44" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
-        <v>1579.576939471672</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P44" t="n">
         <v>2009.555081027735</v>
@@ -7663,28 +7663,28 @@
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W44" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="45">
@@ -7700,7 +7700,7 @@
         <v>452.1903149324157</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E45" t="n">
         <v>78.84709864997603</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1658.367018159816</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1429.292781642309</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1347.095458285568</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U45" t="n">
-        <v>1267.13416483617</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1060.180821299454</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X45" t="n">
-        <v>960.319468324315</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y45" t="n">
-        <v>556.8938190655934</v>
+        <v>732.239087633243</v>
       </c>
     </row>
     <row r="46">
@@ -7821,7 +7821,7 @@
         <v>463.4700425881596</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,19 +7964,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748743</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
         <v>1.159015302735668</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>428.7520804932368</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8216,13 +8216,13 @@
         <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>184.500290865472</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>364.0430754681111</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,10 +8444,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>720.3111720492747</v>
       </c>
       <c r="N8" t="n">
         <v>404.0826666125488</v>
@@ -8456,7 +8456,7 @@
         <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>502.5418702571336</v>
@@ -8681,13 +8681,13 @@
         <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>537.6389720331213</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>628.2994929102651</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L14" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>537.6389720331213</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>248.0013330166451</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>433.9659648939233</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>453.5423549970993</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427137</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>509.0189682897846</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>318.9437086192779</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L32" t="n">
-        <v>430.7657085427137</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M32" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>509.0189682897846</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="M35" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>248.0013330166451</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>679.1243892794788</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N38" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11051,13 +11051,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>950.4344291498551</v>
+        <v>318.9437086192779</v>
       </c>
       <c r="N41" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,22 +11285,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>235.7435709267094</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23417,7 +23417,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495961096</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495925071</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495907059</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24833,13 +24833,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25559,13 +25559,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26036,10 +26036,10 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5614353.185075819</v>
+        <v>5614353.185075818</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6306999.492413528</v>
+        <v>6306999.492413527</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6999645.799751238</v>
+        <v>6999645.799751237</v>
       </c>
     </row>
     <row r="12">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1511252.448399113</v>
+        <v>1511252.448399114</v>
       </c>
       <c r="C2" t="n">
         <v>1511252.448399114</v>
@@ -26287,13 +26287,13 @@
         <v>1511228.306918646</v>
       </c>
       <c r="H2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918645</v>
       </c>
       <c r="I2" t="n">
         <v>1511228.306918646</v>
       </c>
       <c r="J2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918645</v>
       </c>
       <c r="K2" t="n">
         <v>1511228.306918646</v>
@@ -26302,13 +26302,13 @@
         <v>1511228.306918646</v>
       </c>
       <c r="M2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918645</v>
       </c>
       <c r="N2" t="n">
         <v>1511228.306918646</v>
       </c>
       <c r="O2" t="n">
-        <v>1511228.306918645</v>
+        <v>1511228.306918646</v>
       </c>
       <c r="P2" t="n">
         <v>1511228.306918645</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604934</v>
+        <v>466508.6099301391</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>644099.1137323483</v>
+        <v>650600.4786653253</v>
       </c>
       <c r="C6" t="n">
-        <v>877206.0359198373</v>
+        <v>883707.4008528142</v>
       </c>
       <c r="D6" t="n">
-        <v>879217.6833356614</v>
+        <v>885719.048268638</v>
       </c>
       <c r="E6" t="n">
-        <v>357794.778122471</v>
+        <v>364257.7692528248</v>
       </c>
       <c r="F6" t="n">
-        <v>949030.8409406933</v>
+        <v>955493.8320710476</v>
       </c>
       <c r="G6" t="n">
-        <v>950719.2304623469</v>
+        <v>957182.2215927009</v>
       </c>
       <c r="H6" t="n">
-        <v>952409.9633723096</v>
+        <v>958872.9545026629</v>
       </c>
       <c r="I6" t="n">
-        <v>954103.056572857</v>
+        <v>960566.0477032106</v>
       </c>
       <c r="J6" t="n">
-        <v>567350.5271877813</v>
+        <v>573813.5183181344</v>
       </c>
       <c r="K6" t="n">
-        <v>957496.3925666149</v>
+        <v>963959.3836969695</v>
       </c>
       <c r="L6" t="n">
-        <v>959196.6702889587</v>
+        <v>965659.6614193129</v>
       </c>
       <c r="M6" t="n">
-        <v>864099.3781689267</v>
+        <v>870562.3692992801</v>
       </c>
       <c r="N6" t="n">
-        <v>962604.53425969</v>
+        <v>969067.5253900447</v>
       </c>
       <c r="O6" t="n">
-        <v>707512.1568581519</v>
+        <v>713975.1479885065</v>
       </c>
       <c r="P6" t="n">
-        <v>966022.2645097354</v>
+        <v>972485.2556400894</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27005,7 +27005,7 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27014,7 +27014,7 @@
         <v>321</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27518,10 +27518,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27569,16 +27569,16 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
+        <v>26.1959257979226</v>
+      </c>
+      <c r="V3" t="n">
         <v>400</v>
-      </c>
-      <c r="V3" t="n">
-        <v>162.2511894735401</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>290.4416599714519</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27603,19 +27603,19 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>244.8599384153005</v>
+      </c>
+      <c r="H4" t="n">
         <v>400</v>
-      </c>
-      <c r="G4" t="n">
-        <v>400</v>
-      </c>
-      <c r="H4" t="n">
-        <v>342.7808457434555</v>
       </c>
       <c r="I4" t="n">
         <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>214.6636460197994</v>
       </c>
       <c r="K4" t="n">
         <v>267.1509377355693</v>
@@ -27645,19 +27645,19 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,10 +27749,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27767,7 +27767,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>209.5726123064429</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.01292833515062</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>393.9621974156752</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27837,10 +27837,10 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27849,13 +27849,13 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,13 +27882,13 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>395.4276240362839</v>
       </c>
       <c r="U7" t="n">
-        <v>389.5838470077416</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,28 +28031,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>244.9660100705759</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>88.48881128536601</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>274.5727974528598</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28089,13 +28089,13 @@
         <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
-        <v>135.9533008230038</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>388.8706299655965</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
@@ -28232,7 +28232,7 @@
         <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
@@ -28244,7 +28244,7 @@
         <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,31 +28268,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>96.6876464206095</v>
+        <v>321</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28308,7 +28308,7 @@
         <v>321</v>
       </c>
       <c r="D13" t="n">
-        <v>321.0000000000013</v>
+        <v>321</v>
       </c>
       <c r="E13" t="n">
         <v>321</v>
@@ -28460,16 +28460,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>321</v>
@@ -28523,10 +28523,10 @@
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y15" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,10 +28697,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -28709,7 +28709,7 @@
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28754,16 +28754,16 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28903,10 +28903,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28937,16 +28937,16 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -28991,19 +28991,19 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
     </row>
     <row r="22">
@@ -29016,7 +29016,7 @@
         <v>321</v>
       </c>
       <c r="C22" t="n">
-        <v>321.0000000000049</v>
+        <v>321</v>
       </c>
       <c r="D22" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29234,13 +29234,13 @@
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="X24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29319,7 +29319,7 @@
         <v>321</v>
       </c>
       <c r="Y25" t="n">
-        <v>321.0000000000067</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26">
@@ -29347,10 +29347,10 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>147.4081841180273</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29459,7 +29459,7 @@
         <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="T27" t="n">
         <v>321</v>
@@ -29468,16 +29468,16 @@
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29939,13 +29939,13 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>321</v>
@@ -30058,7 +30058,7 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I35" t="n">
         <v>96.76634561233286</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30128,13 +30128,13 @@
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>321</v>
@@ -30164,13 +30164,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>226.036732227374</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="T36" t="n">
         <v>321</v>
@@ -30182,7 +30182,7 @@
         <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>321</v>
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T38" t="n">
         <v>321</v>
@@ -30362,7 +30362,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="E39" t="n">
         <v>321</v>
@@ -30377,7 +30377,7 @@
         <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>96.68764642060964</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
         <v>321</v>
@@ -30422,10 +30422,10 @@
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30596,10 +30596,10 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>96.68764642060943</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30653,16 +30653,16 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43">
@@ -30772,7 +30772,7 @@
         <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,16 +30830,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>321</v>
@@ -30875,13 +30875,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
@@ -30893,7 +30893,7 @@
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>321</v>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
-        <v>373.9999999999999</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>300.2102102361032</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34889,19 +34889,19 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>115.645063904132</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>192.3988611183179</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34931,19 +34931,19 @@
         <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
         <v>64.70900502512563</v>
@@ -34995,13 +34995,13 @@
         <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="P5" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35123,10 +35123,10 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>155.1400615846995</v>
@@ -35135,13 +35135,13 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
         <v>3.798404629106074</v>
@@ -35168,13 +35168,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>186.1889591693704</v>
       </c>
       <c r="U7" t="n">
-        <v>238.6354885201689</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35223,10 +35223,10 @@
         <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -35235,7 +35235,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>242.0199542155221</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35375,13 +35375,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>113.6885159215222</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>141.426984535489</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35460,13 +35460,13 @@
         <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>236.2045428832663</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>397.807439363043</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35475,7 +35475,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35594,7 +35594,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D13" t="n">
-        <v>35.46378194444581</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E13" t="n">
         <v>40.01909516304346</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>236.2045428832663</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35931,7 +35931,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L17" t="n">
         <v>218.2342914572864</v>
@@ -35940,7 +35940,7 @@
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>17.50927946942293</v>
+        <v>649</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,16 +36168,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
         <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>179.1121759491994</v>
+        <v>649</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36302,7 +36302,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C22" t="n">
-        <v>48.27475335196026</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D22" t="n">
         <v>35.46378194444452</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
-        <v>609.8778844919133</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L23" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>223.0503014498772</v>
+      </c>
+      <c r="O23" t="n">
         <v>649</v>
-      </c>
-      <c r="N23" t="n">
-        <v>649</v>
-      </c>
-      <c r="O23" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36605,7 +36605,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y25" t="n">
-        <v>33.5346471505443</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="26">
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L26" t="n">
-        <v>649.0000000000001</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>278.5269147425624</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36885,10 +36885,10 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
-        <v>17.50927946942293</v>
+        <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
-        <v>649.0000000000001</v>
+        <v>649</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>278.5269147425624</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K35" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L35" t="n">
-        <v>218.2342914572864</v>
+        <v>221.895519765053</v>
       </c>
       <c r="M35" t="n">
         <v>649</v>
       </c>
       <c r="N35" t="n">
-        <v>17.50927946942293</v>
+        <v>649</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L38" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M38" t="n">
+        <v>60.29262328527617</v>
+      </c>
+      <c r="N38" t="n">
         <v>649</v>
-      </c>
-      <c r="L38" t="n">
-        <v>649</v>
-      </c>
-      <c r="M38" t="n">
-        <v>377.6899601296238</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37830,13 +37830,13 @@
         <v>649</v>
       </c>
       <c r="L41" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M41" t="n">
+        <v>17.50927946942293</v>
+      </c>
+      <c r="N41" t="n">
         <v>649</v>
-      </c>
-      <c r="M41" t="n">
-        <v>649</v>
-      </c>
-      <c r="N41" t="n">
-        <v>179.1121759491994</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38064,22 +38064,22 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L44" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M44" t="n">
         <v>649</v>
       </c>
-      <c r="L44" t="n">
-        <v>649</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
-        <v>434.3213551071335</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
         <v>592.3686050224903</v>
